--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA6078BA-A747-4D3B-815E-1CE43B8CDBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3541CCD1-E2CD-4C4C-8210-3343A87FE788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="21705" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -60,10 +60,34 @@
     <t>06.02.2026</t>
   </si>
   <si>
-    <t>Setup von Projekt und Github Repo, Angular und Nest basic setup</t>
-  </si>
-  <si>
-    <t>Basic Auth0 Setup, Setup von MongoDB connection und Mongoose + CRUD Funktionalitäten für Technologien implementiert</t>
+    <t>13.02.2026</t>
+  </si>
+  <si>
+    <t>Setup von Projekt und Github Repo</t>
+  </si>
+  <si>
+    <t>Angular und Nest basic setup</t>
+  </si>
+  <si>
+    <t>Mongoose + CRUD Funktionalitäten für Technologien implementiert</t>
+  </si>
+  <si>
+    <t>Setup von MongoDB Atlas connection</t>
+  </si>
+  <si>
+    <t>Basic Auth0 Setup</t>
+  </si>
+  <si>
+    <t>Darstellung des Tech-Radar erstellen</t>
+  </si>
+  <si>
+    <t>Swagger-UI integrieren</t>
+  </si>
+  <si>
+    <t>Technologien imTech-Radar anzeigen</t>
+  </si>
+  <si>
+    <t>14.02.2026</t>
   </si>
 </sst>
 </file>
@@ -99,9 +123,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -440,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5DEABF-7307-41CD-9DD8-6AF6164203B9}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -471,183 +494,149 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
+      <c r="D4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="D5" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="D6" s="3"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="D7" s="3"/>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="D9" s="3"/>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="D10" s="3"/>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="D11" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="D12" s="3"/>
+      <c r="B12" s="1"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="D13" s="3"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="D14" s="3"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="D15" s="3"/>
+      <c r="B15" s="1"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="B16" s="1"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="1"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="1"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="1"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="1"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="1"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="1"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="1"/>
+      <c r="D28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3541CCD1-E2CD-4C4C-8210-3343A87FE788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BF6969-297C-41CA-AD6A-AB9E995DA21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="21705" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
+    <workbookView xWindow="28710" yWindow="4020" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -88,6 +88,12 @@
   </si>
   <si>
     <t>14.02.2026</t>
+  </si>
+  <si>
+    <t>Navbar hinzufügen</t>
+  </si>
+  <si>
+    <t>Auth0 Rolenprüfung bei Zugriff auf Admin-Panel implementieren (lots of problems, gelöst mit custom action in Auth0 welche als custom claim die Rolle auf dem token setzt)</t>
   </si>
 </sst>
 </file>
@@ -568,11 +574,18 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BF6969-297C-41CA-AD6A-AB9E995DA21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F025116E-D20D-4175-9A0E-BC8D0C0AE39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28710" yWindow="4020" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
+    <workbookView xWindow="55290" yWindow="2565" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -94,6 +94,21 @@
   </si>
   <si>
     <t>Auth0 Rolenprüfung bei Zugriff auf Admin-Panel implementieren (lots of problems, gelöst mit custom action in Auth0 welche als custom claim die Rolle auf dem token setzt)</t>
+  </si>
+  <si>
+    <t>15.02.2026</t>
+  </si>
+  <si>
+    <t>Erfassen neuer Technologien im Admin Dashboard implementieren</t>
+  </si>
+  <si>
+    <t>Backend Security implementieren</t>
+  </si>
+  <si>
+    <t>Rollenprüfung im Backend über Guard und Rolle im Access-Token</t>
+  </si>
+  <si>
+    <t>Rollenprüfung im Front nicht mehr via idToken, sondern Access-Token</t>
   </si>
 </sst>
 </file>
@@ -588,20 +603,36 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
-      <c r="D14" s="2"/>
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="D16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
-      <c r="D17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F025116E-D20D-4175-9A0E-BC8D0C0AE39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF2BC62-4CEF-4A66-8420-F9E7AA6B67C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="55290" yWindow="2565" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
+    <workbookView xWindow="33270" yWindow="3015" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -109,6 +109,15 @@
   </si>
   <si>
     <t>Rollenprüfung im Front nicht mehr via idToken, sondern Access-Token</t>
+  </si>
+  <si>
+    <t>16.02.2026</t>
+  </si>
+  <si>
+    <t>Auflistung nicht publizierter Technologien</t>
+  </si>
+  <si>
+    <t>Bearbeitung nicht publizierter Technologien</t>
   </si>
 </sst>
 </file>
@@ -628,53 +637,65 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="D17" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="D28" s="2"/>
     </row>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF2BC62-4CEF-4A66-8420-F9E7AA6B67C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AADE0C3-5CD6-4201-9642-CB58F4A25993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33270" yWindow="3015" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>Bearbeitung nicht publizierter Technologien</t>
+  </si>
+  <si>
+    <t>18.10.2026</t>
   </si>
 </sst>
 </file>
@@ -493,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5DEABF-7307-41CD-9DD8-6AF6164203B9}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -619,7 +622,7 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>20</v>
@@ -664,7 +667,15 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="1"/>
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>1.5</v>
+      </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -698,6 +709,12 @@
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="D28" s="2"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <f>SUM(C3:C20)</f>
+        <v>26.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AADE0C3-5CD6-4201-9642-CB58F4A25993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88D0162-5924-4FF6-84C0-6255D47B36F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33270" yWindow="3015" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -121,6 +121,24 @@
   </si>
   <si>
     <t>18.10.2026</t>
+  </si>
+  <si>
+    <t>Administrator editiert Technologien anstatt diese nur ansehen zu können</t>
+  </si>
+  <si>
+    <t>19.10.2026</t>
+  </si>
+  <si>
+    <t>Tests für Technology Service und Controller im Backend erstellen</t>
+  </si>
+  <si>
+    <t>Überprüfung der Validität der Werte beim erstellen und anpassen von Technologien im Backend implementieren</t>
+  </si>
+  <si>
+    <t>Generelle Überarbeitung der Backend Architektur</t>
+  </si>
+  <si>
+    <t>API Dokumentation implementieren</t>
   </si>
 </sst>
 </file>
@@ -674,25 +692,43 @@
         <v>27</v>
       </c>
       <c r="C20">
-        <v>1.5</v>
-      </c>
-      <c r="D20" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="1"/>
-      <c r="D21" s="2"/>
+      <c r="A21">
+        <v>8</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
-      <c r="D22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
-      <c r="D23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
-      <c r="D24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
@@ -713,7 +749,7 @@
     <row r="37" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C37">
         <f>SUM(C3:C20)</f>
-        <v>26.5</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88D0162-5924-4FF6-84C0-6255D47B36F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3799B5-4AE9-4307-8C46-ACE227AB2A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33270" yWindow="3015" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
+    <workbookView xWindow="58425" yWindow="2385" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -139,6 +139,27 @@
   </si>
   <si>
     <t>API Dokumentation implementieren</t>
+  </si>
+  <si>
+    <t>20.10.2026</t>
+  </si>
+  <si>
+    <t>Statt in allen Komponenten separat die benötigten Technologien laden, den Technologie-Service als Single source of truth verwenden</t>
+  </si>
+  <si>
+    <t>Problem lösen wobei die User-Rolle nicht aus dem Token gelesen werden konnte</t>
+  </si>
+  <si>
+    <t>21.10.2026</t>
+  </si>
+  <si>
+    <t>Ansicht ohne reload updaten wenn sich an den Technologien etwas geändert hat</t>
+  </si>
+  <si>
+    <t>Endlich Testing Setup im Client gefixt</t>
+  </si>
+  <si>
+    <t>Tests für Radar Komponenten und die Edit und Detail Modals, sowie das Form implementieren</t>
   </si>
 </sst>
 </file>
@@ -568,7 +589,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
@@ -615,22 +636,21 @@
       <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="C12">
-        <v>5</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -731,25 +751,54 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
-      <c r="D26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
-      <c r="D27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="1"/>
-      <c r="D28" s="2"/>
+      <c r="A28">
+        <v>10</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D29" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C37">
-        <f>SUM(C3:C20)</f>
-        <v>26</v>
+        <f>SUM(C3:C28)</f>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3799B5-4AE9-4307-8C46-ACE227AB2A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4DBA9F-45D6-4DEF-A3B2-A0733D515FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58425" yWindow="2385" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
+    <workbookView xWindow="34230" yWindow="3450" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -159,7 +159,28 @@
     <t>Endlich Testing Setup im Client gefixt</t>
   </si>
   <si>
-    <t>Tests für Radar Komponenten und die Edit und Detail Modals, sowie das Form implementieren</t>
+    <t>Alle fehlenden Frontend Tests implementieren</t>
+  </si>
+  <si>
+    <t>kleine Improvements im UI</t>
+  </si>
+  <si>
+    <t>Fehlende kleine Features implementiert (Akzeptanzkriterien in Stories erfüllen)</t>
+  </si>
+  <si>
+    <t>22.02.2026</t>
+  </si>
+  <si>
+    <t>Ring und Begründung darf neu leer sein, solange die Technologie noch nicht publiziert ist</t>
+  </si>
+  <si>
+    <t>Neu müssen sich alle User einloggen, um den Technologie Radar zu sehen muss man mindestens die Rolle "Employee" haben</t>
+  </si>
+  <si>
+    <t>Admin User können neu nicht nur das Bearbeitungsformular sehen wenn sie auf eine Technologie klicken, sondern sehen zuerst das Detail und können per Knopfdruck zum Edit wechseln</t>
+  </si>
+  <si>
+    <t>Bei delete gab es einen 404, weil die HTTP Request immer doppelt waren, dies ist jetzt gefixt</t>
   </si>
 </sst>
 </file>
@@ -784,7 +805,7 @@
         <v>37</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>39</v>
@@ -795,10 +816,49 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D30" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D31" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="D34" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D35" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C37">
-        <f>SUM(C3:C28)</f>
-        <v>35</v>
+        <f>SUM(C3:C36)</f>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4DBA9F-45D6-4DEF-A3B2-A0733D515FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28420A30-6655-4F19-95F4-1176CDEA0A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34230" yWindow="3450" windowWidth="19725" windowHeight="15870" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="21705" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -181,6 +181,27 @@
   </si>
   <si>
     <t>Bei delete gab es einen 404, weil die HTTP Request immer doppelt waren, dies ist jetzt gefixt</t>
+  </si>
+  <si>
+    <t>28.02.2026</t>
+  </si>
+  <si>
+    <t>Erste Version der Technische Dokumentation erstellen (Kapitel 1-6)</t>
+  </si>
+  <si>
+    <t>01.03.2026</t>
+  </si>
+  <si>
+    <t>Erste Version der Technische Dokumentation erstellen (Kapitel 7-10)</t>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+  </si>
+  <si>
+    <t>Überarbeitung der technischen Dokumentation</t>
+  </si>
+  <si>
+    <t>Auslagern von Connection-Strings etc. in .env File im Backend</t>
   </si>
 </sst>
 </file>
@@ -556,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5DEABF-7307-41CD-9DD8-6AF6164203B9}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -840,25 +861,63 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="3:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="D34" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D35" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
       <c r="C37">
-        <f>SUM(C3:C36)</f>
-        <v>43</v>
+        <v>3</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D39" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C55">
+        <f>SUM(C3:C50)</f>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28420A30-6655-4F19-95F4-1176CDEA0A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC80B795-6E5D-4955-BF20-F79346EDFA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="21705" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -202,6 +202,18 @@
   </si>
   <si>
     <t>Auslagern von Connection-Strings etc. in .env File im Backend</t>
+  </si>
+  <si>
+    <t>04.03.2026</t>
+  </si>
+  <si>
+    <t>Kleine Improvements und Quality of Life fixes</t>
+  </si>
+  <si>
+    <t>Bugfix -&gt; Bei Edit von Technologies wurde leer setzen von Reason oder Ring nicht registriert</t>
+  </si>
+  <si>
+    <t>MongoDB Docker Image mit initialen Daten erstellen als Ersatz für die nicht mehr verwendete Atlas MongoDB</t>
   </si>
 </sst>
 </file>
@@ -914,10 +926,31 @@
         <v>54</v>
       </c>
     </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D41" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D42" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
     <row r="55" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C55">
         <f>SUM(C3:C50)</f>
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC80B795-6E5D-4955-BF20-F79346EDFA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91BF378-186D-45BB-9BFF-5D3AC81B5BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="21705" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="38610" windowHeight="21705" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -214,6 +214,24 @@
   </si>
   <si>
     <t>MongoDB Docker Image mit initialen Daten erstellen als Ersatz für die nicht mehr verwendete Atlas MongoDB</t>
+  </si>
+  <si>
+    <t>05.03.2026</t>
+  </si>
+  <si>
+    <t>Techradar SVG Darstellung durch Liste ersetzen</t>
+  </si>
+  <si>
+    <t>Navbar und Edit-Modal</t>
+  </si>
+  <si>
+    <t>Responsive machen was noch nicht responsive ist  (Techradar SVG Darstellung durch Liste ersetzen)</t>
+  </si>
+  <si>
+    <t>Improper Teardown warning vom Mongo Memory Server fixen in Tests</t>
+  </si>
+  <si>
+    <t>Installation Step-by-Step in README.md erstellen</t>
   </si>
 </sst>
 </file>
@@ -589,12 +607,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5DEABF-7307-41CD-9DD8-6AF6164203B9}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="118.7109375" customWidth="1"/>
+    <col min="5" max="5" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -867,28 +886,31 @@
         <v>43</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="D34" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D35" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>12</v>
+      </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
@@ -899,7 +921,10 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>13</v>
+      </c>
       <c r="B37" t="s">
         <v>50</v>
       </c>
@@ -910,23 +935,29 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>14</v>
+      </c>
       <c r="B38" t="s">
         <v>52</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D39" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>15</v>
+      </c>
       <c r="B40" t="s">
         <v>55</v>
       </c>
@@ -937,20 +968,57 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D41" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D42" s="2" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E46" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C55">
         <f>SUM(C3:C50)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hslu\5\HSLU-WEBLAB-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91BF378-186D-45BB-9BFF-5D3AC81B5BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308D639E-25B5-4988-B3BE-C88D11F9D318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="38610" windowHeight="21705" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="21705" xr2:uid="{8963AE09-82EA-400C-87CD-5BBEBCD543DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Arbeitsjournal</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Datum</t>
   </si>
   <si>
-    <t>Kommentar</t>
-  </si>
-  <si>
     <t>04.02.2026</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
     <t>18.10.2026</t>
   </si>
   <si>
-    <t>Administrator editiert Technologien anstatt diese nur ansehen zu können</t>
-  </si>
-  <si>
     <t>19.10.2026</t>
   </si>
   <si>
@@ -219,26 +213,59 @@
     <t>05.03.2026</t>
   </si>
   <si>
-    <t>Techradar SVG Darstellung durch Liste ersetzen</t>
-  </si>
-  <si>
-    <t>Navbar und Edit-Modal</t>
-  </si>
-  <si>
-    <t>Responsive machen was noch nicht responsive ist  (Techradar SVG Darstellung durch Liste ersetzen)</t>
-  </si>
-  <si>
     <t>Improper Teardown warning vom Mongo Memory Server fixen in Tests</t>
   </si>
   <si>
     <t>Installation Step-by-Step in README.md erstellen</t>
+  </si>
+  <si>
+    <t>Responsiveness: Techradar SVG Darstellung durch Liste ersetzen bei kleinen Screen</t>
+  </si>
+  <si>
+    <t>Responsiveness: Side Scroll bei Edit-Modal verhindern</t>
+  </si>
+  <si>
+    <t>Responsiveness: Schriftzüge durch Icons ersetzen in Navbar</t>
+  </si>
+  <si>
+    <t>Kommentare</t>
+  </si>
+  <si>
+    <t>Administrator editiert publizierte Technologien anstatt diese nur ansehen zu können</t>
+  </si>
+  <si>
+    <t>Versuchen Frontend Testing zum laufen zu bringen</t>
+  </si>
+  <si>
+    <t>Probleme mit Frontend Testing fixen</t>
+  </si>
+  <si>
+    <t>06.03.2026</t>
+  </si>
+  <si>
+    <t>Finale Überarbeitung der arc42-Dokumentation</t>
+  </si>
+  <si>
+    <t>Fazit &amp; Refelxion schreiben</t>
+  </si>
+  <si>
+    <t>Arbeitsjournal finalisieren</t>
+  </si>
+  <si>
+    <t>Letzter Abgleich mit Anforderungen</t>
+  </si>
+  <si>
+    <t>Abgabe :)</t>
+  </si>
+  <si>
+    <t>Gesamtaufwand (h)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,13 +273,55 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -264,17 +333,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Gut" xfId="1" builtinId="26"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -607,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5DEABF-7307-41CD-9DD8-6AF6164203B9}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -616,409 +692,480 @@
     <col min="5" max="5" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C7">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" t="s">
+      <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>4</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="1"/>
-      <c r="D15" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="1"/>
-      <c r="D16" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="D17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+      <c r="D20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+      <c r="D21" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>6</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="1"/>
-      <c r="D19" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>7</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>8</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
       <c r="D22" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-      <c r="D23" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="1"/>
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>9</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
+      <c r="B25" s="1"/>
       <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B26" s="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="1"/>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+      <c r="D31" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+      <c r="D32" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+      <c r="D33" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>9</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B36" s="1"/>
+      <c r="D36" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="1"/>
+      <c r="D37" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>10</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39">
+        <v>5</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C28">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D40" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D41" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D42" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44">
+        <v>6</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D45" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="D46" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D47" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>14</v>
+      </c>
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D54" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56">
+        <v>4</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D57" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D58" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>16</v>
+      </c>
+      <c r="B60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D61" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>17</v>
+      </c>
+      <c r="B66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66">
         <v>5</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D29" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D30" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D31" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32">
-        <v>6</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D33" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="D34" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D35" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>12</v>
-      </c>
-      <c r="B36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>13</v>
-      </c>
-      <c r="B37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37">
-        <v>3</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>14</v>
-      </c>
-      <c r="B38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D39" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D41" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D42" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>16</v>
-      </c>
-      <c r="B43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43">
-        <v>3</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E46" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D48" t="s">
+      <c r="D66" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C72" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C73" s="7">
+        <f>SUM(C4:C66)</f>
         <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C55">
-        <f>SUM(C3:C50)</f>
-        <v>59</v>
       </c>
     </row>
   </sheetData>
